--- a/HK_Swing_Pattern.xlsx
+++ b/HK_Swing_Pattern.xlsx
@@ -27170,9 +27170,7 @@
       </c>
       <c r="O426" s="2" t="inlineStr"/>
       <c r="P426" s="2" t="inlineStr"/>
-      <c r="Q426" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q426" s="2" t="inlineStr"/>
       <c r="R426" s="2" t="n">
         <v>-1</v>
       </c>
@@ -33286,7 +33284,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    阳线path: 中大阳(实体&gt;3% ∨ 收盘较昨收&gt;3%, 覆盖大幅低开高走) + 收盘位于日内上1/3 + 放量(&gt;=1.8x 20日均量) + 当日涨幅较指数超额&gt;=2%(A股沪深300/HK恒指HSI.HI(jianxin)/美股S&amp;P500; 基准缺失时跳过此门)</t>
+          <t xml:space="preserve">    阳线path: 中大阳(实体&gt;3% ∨ 收盘较昨收&gt;3%, 覆盖大幅低开高走) + 收盘位于日内上1/3 + 放量(&gt;=1.8x 20日均量) + 当日涨幅较指数超额&gt;=2%(A股沪深300指数000300.SH/HK恒指HSI.HI/美股标普500指数^GSPC, 均首选jianxin真实指数, ETF兜底; 基准缺失时跳过此门)</t>
         </is>
       </c>
     </row>

--- a/HK_Swing_Pattern.xlsx
+++ b/HK_Swing_Pattern.xlsx
@@ -1877,9 +1877,7 @@
         <v>3</v>
       </c>
       <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr"/>
       <c r="R21" s="2" t="inlineStr"/>
       <c r="S21" s="2" t="inlineStr"/>
@@ -15399,9 +15397,7 @@
         <v>0</v>
       </c>
       <c r="O233" s="2" t="inlineStr"/>
-      <c r="P233" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="P233" s="2" t="inlineStr"/>
       <c r="Q233" s="2" t="inlineStr"/>
       <c r="R233" s="2" t="n">
         <v>1</v>
@@ -30432,9 +30428,7 @@
       </c>
       <c r="O473" s="2" t="inlineStr"/>
       <c r="P473" s="2" t="inlineStr"/>
-      <c r="Q473" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q473" s="2" t="inlineStr"/>
       <c r="R473" s="2" t="inlineStr"/>
       <c r="S473" s="2" t="inlineStr"/>
       <c r="T473" s="2" t="inlineStr"/>
@@ -31649,9 +31643,7 @@
       <c r="O494" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P494" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="P494" s="2" t="inlineStr"/>
       <c r="Q494" s="2" t="inlineStr"/>
       <c r="R494" s="2" t="inlineStr"/>
       <c r="S494" s="2" t="inlineStr"/>
@@ -33663,14 +33655,14 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SOS (Sign of Strength, Wyckoff): P1前置(位置门前): {C&gt;MA5, C&gt;MA10, MA5&gt;MA10}三项比较至少2项为正(排除股价在短期均线下方/空头排列)。位置门 = A OR B。A: 200日pos&lt;=0.80(200日数据不足回退3个月); B: 近3日 4均线(5/10/15/20)纠缠 max/min-1&lt;5%。强度: 放量+RS超额+阳线。捕获纠缠平台突破、次新股底部反强</t>
+          <t xml:space="preserve">  SOS (Sign of Strength, Wyckoff): P1前置(位置门前): {C&gt;MA5, C&gt;MA10, MA5&gt;MA10}三项比较至少2项为正(排除股价在短期均线下方/空头排列)。位置门 = A OR B。A: 200日pos&lt;=0.80(200日数据不足回退3个月); B: 近3日 4均线(5/10/15/20)纠缠 max/min-1&lt;5% 且距250日收盘高点回落≥5%(创新高处的平台突破归新高, 不算SOS)。仙股过滤: 信号K线收盘&lt;0.5(本币)不触发。强度: 放量+RS超额+阳线。捕获纠缠平台突破、次新股底部反强</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    阳线path: 中大阳(实体&gt;3% ∨ 收盘较昨收&gt;3%, 覆盖大幅低开高走) + 收盘位于日内上1/3 + 放量(&gt;=1.8x 20日均量) + 当日涨幅较指数超额&gt;=2%(A股沪深300指数000300.SH/HK恒指HSI.HI/美股标普500指数^GSPC, 均首选jianxin真实指数, ETF兜底; 基准缺失时跳过此门)</t>
+          <t xml:space="preserve">    阳线path: 中大阳(实体&gt;3% ∨ 收盘较昨收&gt;3%, 覆盖大幅低开高走) + 收盘位于日内上1/3 + 放量(&gt;=2x 20日均量) + 当日涨幅较指数超额&gt;=2%(A股沪深300指数000300.SH/HK恒指HSI.HI/美股标普500指数^GSPC, 均首选jianxin真实指数, ETF兜底; 基准缺失时跳过此门)</t>
         </is>
       </c>
     </row>
